--- a/GitPractice/src/test/resources/TestscriptDataforutility.xlsx
+++ b/GitPractice/src/test/resources/TestscriptDataforutility.xlsx
@@ -3,19 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\SeleniumData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13545" windowHeight="6135" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
     <sheet name="contacts" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="36">
   <si>
     <t>TestCase_Id</t>
   </si>
@@ -94,6 +91,45 @@
   </si>
   <si>
     <t>tc_06</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>vidya</t>
+  </si>
+  <si>
+    <t>Shree1</t>
+  </si>
+  <si>
+    <t>Shree2</t>
+  </si>
+  <si>
+    <t>Shree3</t>
+  </si>
+  <si>
+    <t>Shree4</t>
+  </si>
+  <si>
+    <t>Shree5</t>
+  </si>
+  <si>
+    <t>Shree6</t>
+  </si>
+  <si>
+    <t>Shree7</t>
+  </si>
+  <si>
+    <t>Shree8</t>
+  </si>
+  <si>
+    <t>Shree9</t>
+  </si>
+  <si>
+    <t>Shree10</t>
   </si>
 </sst>
 </file>
@@ -615,4 +651,102 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>